--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513092_ELIMINATORIAS14FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513092_ELIMINATORIAS14FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8692</v>
+        <v>5.5468</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6828</v>
+        <v>3.2333</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1865</v>
+        <v>2.3135</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5966</v>
+        <v>4.6179</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0901</v>
+        <v>1.1061</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5065</v>
+        <v>3.5118</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7253</v>
+        <v>3.8134</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9826</v>
+        <v>2.0334</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7427</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8713</v>
+        <v>0.8046</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8925</v>
+        <v>-0.9273</v>
       </c>
       <c r="O2" t="n">
-        <v>1.7638</v>
+        <v>1.7318</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.908</v>
+        <v>-1.2613</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.441</v>
+        <v>-1.009</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4671</v>
+        <v>-0.2523</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3482</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.568</v>
+        <v>3.8061</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9476</v>
+        <v>4.0441</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6203</v>
+        <v>-0.238</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5451</v>
+        <v>5.0897</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6195</v>
+        <v>-1.3036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9256</v>
+        <v>6.3933</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7851</v>
+        <v>4.3231</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2052</v>
+        <v>-0.4945</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4202</v>
+        <v>4.8176</v>
       </c>
       <c r="M3" t="n">
-        <v>0.76</v>
+        <v>0.7667</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5857</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3458</v>
+        <v>1.5757</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2291</v>
+        <v>0.8098</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8794999999999999</v>
+        <v>-0.4861</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2801</v>
+        <v>-0.4569</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5994</v>
+        <v>-0.0292</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9385</v>
+        <v>-0.5951</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9068</v>
+        <v>1.1902</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-1.7853</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2502</v>
+        <v>3.7334</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5086</v>
+        <v>2.5103</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2584</v>
+        <v>1.2231</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0899</v>
+        <v>2.5236</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2825</v>
+        <v>1.6208</v>
       </c>
       <c r="I4" t="n">
-        <v>6.3724</v>
+        <v>0.9028</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2692</v>
+        <v>1.8185</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5016</v>
+        <v>2.2323</v>
       </c>
       <c r="L4" t="n">
-        <v>4.7708</v>
+        <v>-0.4138</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8207</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7809</v>
+        <v>-0.6115</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6016</v>
+        <v>1.3166</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8194</v>
+        <v>1.2147</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0446</v>
+        <v>0.068</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.917</v>
+        <v>-0.239</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1276</v>
+        <v>0.307</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5903</v>
+        <v>0.9393</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1806</v>
+        <v>1.943</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7709</v>
+        <v>-1.0037</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7092</v>
+        <v>2.151</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3148</v>
+        <v>2.7766</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6055</v>
+        <v>-0.6256</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0222</v>
+        <v>1.0011</v>
       </c>
       <c r="H5" t="n">
-        <v>0.315</v>
+        <v>0.3162</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.6848</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0425</v>
+        <v>1.0673</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8449</v>
+        <v>0.8686</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1976</v>
+        <v>0.1988</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0203</v>
+        <v>-0.0663</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5299</v>
+        <v>-0.5523</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5097</v>
+        <v>0.4861</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7932</v>
+        <v>0.2432</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6075</v>
+        <v>0.0172</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1857</v>
+        <v>0.226</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6647</v>
+        <v>1.6921</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3626</v>
+        <v>1.8928</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3741</v>
+        <v>2.8771</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0115</v>
+        <v>-0.9843</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4018</v>
+        <v>0.3959</v>
       </c>
       <c r="H6" t="n">
-        <v>1.059</v>
+        <v>1.0482</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="J6" t="n">
-        <v>1.783</v>
+        <v>1.8237</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9515</v>
+        <v>1.9755</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1685</v>
+        <v>-0.1518</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3812</v>
+        <v>-1.4278</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8925</v>
+        <v>-0.9273</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4887</v>
+        <v>-0.5006</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0392</v>
+        <v>-0.5031</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5895</v>
+        <v>-0.1368</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4497</v>
+        <v>-0.3663</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.138</v>
+        <v>1.6045</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8322000000000001</v>
+        <v>1.2151</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3057</v>
+        <v>0.3894</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1834</v>
+        <v>0.1742</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1734</v>
+        <v>1.1666</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.99</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1101</v>
+        <v>0.1374</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4246</v>
+        <v>1.4421</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3145</v>
+        <v>-1.3047</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0733</v>
+        <v>0.0367</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2512</v>
+        <v>-0.2755</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3245</v>
+        <v>0.3122</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8034</v>
+        <v>-0.3187</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4585</v>
+        <v>-0.1125</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3449</v>
+        <v>-0.2062</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9385</v>
+        <v>0.9393</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5141</v>
+        <v>0.3041</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7494</v>
+        <v>-0.8615</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2636</v>
+        <v>1.1656</v>
       </c>
       <c r="G8" t="n">
-        <v>2.427</v>
+        <v>2.4197</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4263</v>
+        <v>0.4157</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0008</v>
+        <v>2.004</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9538</v>
+        <v>1.9829</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3465</v>
+        <v>1.3631</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6072</v>
+        <v>0.6198</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4733</v>
+        <v>0.4367</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9203</v>
+        <v>-0.9474</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3935</v>
+        <v>1.3842</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0935</v>
+        <v>-0.3058</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0418</v>
+        <v>-0.1316</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1353</v>
+        <v>-0.1742</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1062</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0451</v>
+        <v>-0.0422</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7035</v>
+        <v>-1.8705</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6585</v>
+        <v>1.8283</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0718</v>
+        <v>0.0635</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5359</v>
+        <v>-1.5416</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6077</v>
+        <v>1.605</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2366</v>
+        <v>0.2894</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9779</v>
+        <v>-0.9502</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2145</v>
+        <v>1.2396</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1648</v>
+        <v>-0.226</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5913</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3932</v>
+        <v>0.3654</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1737</v>
+        <v>0.1698</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.048</v>
+        <v>-0.3133</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2217</v>
+        <v>0.4831</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9385</v>
+        <v>0.9393</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3572</v>
+        <v>-1.7424</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2713</v>
+        <v>0.2581</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.086</v>
+        <v>-2.0005</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3358</v>
+        <v>-1.3316</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5464</v>
+        <v>0.5531</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8822</v>
+        <v>-1.8847</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0101</v>
+        <v>0.0559</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0802</v>
+        <v>2.1322</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0903</v>
+        <v>-2.0763</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3257</v>
+        <v>-1.3875</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5338</v>
+        <v>-1.5791</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2081</v>
+        <v>0.1915</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6602</v>
+        <v>-1.0304</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8515</v>
+        <v>-0.3929</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8088</v>
+        <v>-0.6375</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8028</v>
+        <v>-2.4764</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8753</v>
+        <v>-2.6478</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0726</v>
+        <v>0.1714</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9347</v>
+        <v>-2.9446</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4168</v>
+        <v>-2.4307</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5179</v>
+        <v>-0.5139</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3767</v>
+        <v>-2.3533</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0227</v>
+        <v>-1.0088</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.354</v>
+        <v>-1.3444</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5913</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3941</v>
+        <v>-1.4218</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8361</v>
+        <v>0.8305</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2535</v>
+        <v>-0.9244</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.655</v>
+        <v>-0.4725</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5985</v>
+        <v>-0.452</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4758</v>
+        <v>-3.4246</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8555</v>
+        <v>-3.7535</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3797</v>
+        <v>0.3289</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0808</v>
+        <v>1.0641</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5379</v>
+        <v>0.5339</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5429</v>
+        <v>0.5302</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8997</v>
+        <v>1.9358</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8207</v>
+        <v>1.8563</v>
       </c>
       <c r="L12" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8189</v>
+        <v>-0.8717</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2828</v>
+        <v>-1.3224</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4639</v>
+        <v>0.4507</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4824</v>
+        <v>-3.4417</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7259</v>
+        <v>-0.7029</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2857</v>
+        <v>-0.2839</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4402</v>
+        <v>-0.419</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.730400000000001</v>
+        <v>11.3531</v>
       </c>
       <c r="E13" t="n">
-        <v>5.205099999999997</v>
+        <v>7.781299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>4.525499999999999</v>
+        <v>3.5718</v>
       </c>
       <c r="G13" t="n">
-        <v>13.1481</v>
+        <v>13.0735</v>
       </c>
       <c r="H13" t="n">
-        <v>1.532400000000001</v>
+        <v>1.484700000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>11.6158</v>
+        <v>11.5886</v>
       </c>
       <c r="J13" t="n">
-        <v>14.4185</v>
+        <v>14.8941</v>
       </c>
       <c r="K13" t="n">
-        <v>11.154</v>
+        <v>11.45</v>
       </c>
       <c r="L13" t="n">
-        <v>3.2643</v>
+        <v>3.4443</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2703</v>
+        <v>-1.8208</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.621699999999999</v>
+        <v>-9.9649</v>
       </c>
       <c r="O13" t="n">
-        <v>8.351500000000001</v>
+        <v>8.1441</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.3392</v>
+        <v>-14.1718</v>
       </c>
       <c r="R13" t="n">
-        <v>12.2909</v>
+        <v>12.1471</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.6819</v>
+        <v>-5.0517</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.316800000000001</v>
+        <v>-3.5312</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3653</v>
+        <v>-1.5206</v>
       </c>
       <c r="V13" t="n">
-        <v>5.3126</v>
+        <v>5.356</v>
       </c>
       <c r="W13" t="n">
-        <v>10.4428</v>
+        <v>10.5898</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.130100000000001</v>
+        <v>-5.2338</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.911</v>
+        <v>3.7466</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2879</v>
+        <v>2.3733</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3768</v>
+        <v>1.3733</v>
       </c>
       <c r="G14" t="n">
-        <v>1.891</v>
+        <v>1.7381</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9991</v>
+        <v>1.2256</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1081</v>
+        <v>0.5125</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2774</v>
+        <v>2.055</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1983</v>
+        <v>1.9755</v>
       </c>
       <c r="L14" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3863</v>
+        <v>-0.3169</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1992</v>
+        <v>-0.7499</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1871</v>
+        <v>0.433</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8194</v>
+        <v>1.4172</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2291</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0485</v>
+        <v>1.4172</v>
       </c>
       <c r="S14" t="n">
-        <v>2.909</v>
+        <v>0.5913</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8784</v>
+        <v>0.3183</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0306</v>
+        <v>0.2731</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7084</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3612</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.0696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0308</v>
+        <v>3.3059</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5066</v>
+        <v>5.2629</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5243</v>
+        <v>-1.957</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7464</v>
+        <v>1.9077</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2264</v>
+        <v>2.0342</v>
       </c>
       <c r="I15" t="n">
-        <v>0.52</v>
+        <v>-0.1265</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0305</v>
+        <v>3.3568</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9515</v>
+        <v>3.2773</v>
       </c>
       <c r="L15" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2841</v>
+        <v>-1.4491</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7251</v>
+        <v>-1.2431</v>
       </c>
       <c r="O15" t="n">
-        <v>0.441</v>
+        <v>-0.206</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4339</v>
+        <v>0.8098</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.2147</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4339</v>
+        <v>2.0245</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1495</v>
+        <v>1.3025</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.524</v>
+        <v>0.7403</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3745</v>
+        <v>0.5622</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.7141</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.3804</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-3.0945</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0996</v>
+        <v>1.1346</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1247</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0251</v>
+        <v>0.1532</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9772</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0813</v>
+        <v>-1.0681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.104</v>
+        <v>0.0958</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8598</v>
+        <v>0.9146</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1735</v>
+        <v>0.2153</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6863</v>
+        <v>0.6993</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.837</v>
+        <v>-1.887</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2548</v>
+        <v>-1.2834</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.6036</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2434</v>
+        <v>1.2505</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7474</v>
+        <v>0.5084</v>
       </c>
       <c r="U16" t="n">
-        <v>0.496</v>
+        <v>0.742</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6528</v>
+        <v>1.6663</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4835</v>
+        <v>0.902</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7081</v>
+        <v>-0.4387</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7754</v>
+        <v>1.3407</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9761</v>
+        <v>0.87</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6632</v>
+        <v>0.9687</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.6393</v>
+        <v>-0.0987</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6784</v>
+        <v>0.4144</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0296</v>
+        <v>1.0668</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.708</v>
+        <v>-0.6523</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2976</v>
+        <v>0.4556</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3664</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0687</v>
+        <v>0.5537</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6388</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q17" t="n">
+        <v>-1.0123</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="V17" t="n">
         <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.6388</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.5469</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.3865</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.1604</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-0.7262</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.308</v>
+        <v>0.3032</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8897</v>
+        <v>0.0316</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1976</v>
+        <v>0.2716</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8701</v>
+        <v>-1.9829</v>
       </c>
       <c r="H18" t="n">
-        <v>0.97</v>
+        <v>0.6528</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0998</v>
+        <v>-2.6357</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3966</v>
+        <v>-0.6343</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0538</v>
+        <v>2.0545</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6572</v>
+        <v>-2.6889</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4736</v>
+        <v>-1.3486</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0838</v>
+        <v>-1.4017</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5574</v>
+        <v>0.0531</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2048</v>
+        <v>1.6196</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8194</v>
+        <v>1.6196</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3573</v>
+        <v>1.4193</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.262</v>
+        <v>0.6659</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0953</v>
+        <v>0.7533</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.7528</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4497</v>
+        <v>-0.4702</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7065</v>
+        <v>-0.2006</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1562</v>
+        <v>-0.2696</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4909</v>
+        <v>-1.5331</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6745</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.1654</v>
+        <v>-1.6123</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3315</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2638</v>
+        <v>1.6192</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9322</v>
+        <v>-0.6288</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8224</v>
+        <v>-2.5235</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5893</v>
+        <v>-1.5401</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2332</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2291</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2048</v>
+        <v>-2.4294</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4339</v>
+        <v>1.6196</v>
       </c>
       <c r="S19" t="n">
-        <v>2.341</v>
+        <v>0.2997</v>
       </c>
       <c r="T19" t="n">
-        <v>0.928</v>
+        <v>-0.4537</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4129</v>
+        <v>0.7533</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5288</v>
+        <v>1.573</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3482</v>
+        <v>1.6921</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1806</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6424</v>
+        <v>-1.7527</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2739</v>
+        <v>-0.1622</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3685</v>
+        <v>-1.5905</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5164</v>
+        <v>-2.5053</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0808</v>
+        <v>0.6722</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5972</v>
+        <v>-3.1775</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9438</v>
+        <v>0.3743</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5865</v>
+        <v>2.2916</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6427</v>
+        <v>-1.9173</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4602</v>
+        <v>-2.8796</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5057</v>
+        <v>-1.6194</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9545</v>
+        <v>-1.2602</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8194</v>
+        <v>1.2147</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4582</v>
+        <v>-0.2025</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6388</v>
+        <v>1.4172</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8532999999999999</v>
+        <v>1.0723</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4242</v>
+        <v>0.0101</v>
       </c>
       <c r="U20" t="n">
-        <v>0.571</v>
+        <v>1.0622</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5467</v>
+        <v>-1.5344</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6647</v>
+        <v>-0.3442</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1181</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7605</v>
+        <v>-3.5319</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4311</v>
+        <v>-3.3476</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3294</v>
+        <v>-0.1843</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3293</v>
+        <v>-1.3233</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3122</v>
+        <v>-0.3161</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0171</v>
+        <v>-1.0072</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.101</v>
+        <v>-1.0655</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3571</v>
+        <v>0.3747</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.458</v>
+        <v>-1.4402</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2283</v>
+        <v>-0.2578</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6693</v>
+        <v>-0.6908</v>
       </c>
       <c r="O21" t="n">
-        <v>0.441</v>
+        <v>0.433</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2281</v>
+        <v>0.4313</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1728</v>
+        <v>0.1798</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0553</v>
+        <v>0.2514</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.635</v>
+        <v>-1.6276</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4544</v>
+        <v>-0.4374</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8167</v>
+        <v>-4.0224</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3969</v>
+        <v>-3.6008</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4198</v>
+        <v>-0.4216</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9226</v>
+        <v>-4.9196</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.1031</v>
+        <v>-4.1112</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8195</v>
+        <v>-0.8085</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.5743</v>
+        <v>-3.5332</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.709</v>
+        <v>-2.6893</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8653</v>
+        <v>-0.8439</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3483</v>
+        <v>-1.3864</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3941</v>
+        <v>-1.4218</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0458</v>
+        <v>0.0354</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7146</v>
+        <v>0.077</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.655</v>
+        <v>0.0864</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0596</v>
+        <v>-0.0094</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8205</v>
+        <v>0.8202</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X22" t="n">
-        <v>0.5784</v>
+        <v>0.5693</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0409</v>
+        <v>-4.3868</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0201</v>
+        <v>-1.6034</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0208</v>
+        <v>-2.7834</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9835</v>
+        <v>-1.3874</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5691</v>
+        <v>-0.0603</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4143</v>
+        <v>-1.327</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1603</v>
+        <v>1.077</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.374</v>
+        <v>1.1438</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7863</v>
+        <v>-0.0668</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8232</v>
+        <v>-2.4644</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1952</v>
+        <v>-1.2041</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.628</v>
+        <v>-1.2602</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4097</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2048</v>
+        <v>-2.4294</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6145</v>
+        <v>1.8221</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5603</v>
+        <v>0.4515</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.655</v>
+        <v>-0.1578</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0946</v>
+        <v>0.6093</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.9068</v>
+        <v>-2.8436</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.9068</v>
+        <v>-2.7504</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8533</v>
+        <v>-4.9806</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8474</v>
+        <v>-2.8677</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0059</v>
+        <v>-2.1129</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4597</v>
+        <v>-2.9653</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0805</v>
+        <v>-1.562</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3792</v>
+        <v>-1.4033</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9447</v>
+        <v>-2.1288</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0907</v>
+        <v>-1.3644</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.146</v>
+        <v>-0.7644</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4044</v>
+        <v>-0.8365</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1712</v>
+        <v>-0.1975</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2332</v>
+        <v>-0.639</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6145</v>
+        <v>0.4049</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4582</v>
+        <v>-0.2025</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8436</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9515</v>
+        <v>-0.4772</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2277</v>
+        <v>-0.5365</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2762</v>
+        <v>0.0593</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8275</v>
+        <v>-1.943</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1062</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.7213</v>
+        <v>-1.943</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.730600000000001</v>
+        <v>-9.752299999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.525300000000001</v>
+        <v>-3.5718</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.2052</v>
+        <v>-6.180499999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-13.1482</v>
+        <v>-13.0734</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.5322</v>
+        <v>-1.485</v>
       </c>
       <c r="I25" t="n">
-        <v>-11.6159</v>
+        <v>-11.5884</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2703</v>
+        <v>1.8207</v>
       </c>
       <c r="K25" t="n">
-        <v>9.6218</v>
+        <v>9.965000000000002</v>
       </c>
       <c r="L25" t="n">
-        <v>-8.3514</v>
+        <v>-8.144299999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-14.4182</v>
+        <v>-14.8942</v>
       </c>
       <c r="N25" t="n">
-        <v>-11.1541</v>
+        <v>-11.4499</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.2643</v>
+        <v>-3.444199999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>2.0486</v>
+        <v>2.0244</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.2908</v>
+        <v>-12.1472</v>
       </c>
       <c r="R25" t="n">
-        <v>14.3392</v>
+        <v>14.1718</v>
       </c>
       <c r="S25" t="n">
-        <v>6.6819</v>
+        <v>6.6527</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3652</v>
+        <v>1.5203</v>
       </c>
       <c r="U25" t="n">
-        <v>5.3166</v>
+        <v>5.132</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.3127</v>
+        <v>-5.356</v>
       </c>
       <c r="W25" t="n">
-        <v>5.1301</v>
+        <v>5.233899999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-10.4429</v>
+        <v>-10.5898</v>
       </c>
     </row>
   </sheetData>
